--- a/docs/publications/close-2025/rate-buildup.xlsx
+++ b/docs/publications/close-2025/rate-buildup.xlsx
@@ -490,7 +490,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period 2025 · prepared 2026-09-15 14:38 UTC</t>
+          <t>Period 2025 · prepared 2026-09-15 14:43 UTC</t>
         </is>
       </c>
     </row>

--- a/docs/publications/close-2025/rate-buildup.xlsx
+++ b/docs/publications/close-2025/rate-buildup.xlsx
@@ -37,10 +37,10 @@
       <sz val="9"/>
     </font>
     <font>
-      <b val="1"/>
+      <sz val="10"/>
     </font>
     <font>
-      <sz val="10"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -68,17 +68,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -93,7 +90,7 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -490,483 +487,483 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period 2025 · prepared 2026-09-15 14:43 UTC</t>
+          <t>Period 2025 · prepared 2026-09-17 09:27 UTC</t>
         </is>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>CERTIFIED — Tom Metzinger, 15 Sep 2026.</t>
+          <t>REHEARSAL — NOT CERTIFIED. A drive produced this signature to prove the mechanism; no person gave it.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>The signature records what was unfinished when it was given, and those steps are part of it: The paper behind the judgments, The position on each invoice.</t>
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Nothing resting on it may be sent to a sponsor. The rate itself is arithmetic and stands; what is missing is somebody putting their name to it.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>Rate</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>Pool</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>Base amount</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>Rate</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>Sealed by</t>
         </is>
       </c>
-      <c r="H8" s="5" t="inlineStr">
+      <c r="H8" s="4" t="inlineStr">
         <is>
           <t>Sealed at</t>
         </is>
       </c>
-      <c r="I8" s="5" t="inlineStr">
+      <c r="I8" s="4" t="inlineStr">
         <is>
           <t>Seal</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>FRINGE</t>
         </is>
       </c>
-      <c r="B9" s="7" t="n">
+      <c r="B9" s="6" t="n">
         <v>401783.6</v>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>SALARIES_WAGES</t>
         </is>
       </c>
-      <c r="D9" s="7" t="n">
+      <c r="D9" s="6" t="n">
         <v>1835047.17</v>
       </c>
-      <c r="E9" s="8" t="n">
+      <c r="E9" s="7" t="n">
         <v>0.219</v>
       </c>
-      <c r="F9" s="6" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>Tom Metzinger</t>
         </is>
       </c>
-      <c r="H9" s="9" t="n">
+      <c r="H9" s="8" t="n">
         <v>46277.95163776228</v>
       </c>
-      <c r="I9" s="6" t="inlineStr">
+      <c r="I9" s="5" t="inlineStr">
         <is>
           <t>60fb3f4b52219514d8f0dc8d20c962ad2fd902dee0cf2407da91f2a93d215a37</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>OVERHEAD</t>
         </is>
       </c>
-      <c r="B10" s="7" t="n">
+      <c r="B10" s="6" t="n">
         <v>584774.52</v>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>MTDC</t>
         </is>
       </c>
-      <c r="D10" s="7" t="n">
+      <c r="D10" s="6" t="n">
         <v>4736602.11</v>
       </c>
-      <c r="E10" s="8" t="n">
+      <c r="E10" s="7" t="n">
         <v>0.1235</v>
       </c>
-      <c r="F10" s="6" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>Tom Metzinger</t>
         </is>
       </c>
-      <c r="H10" s="9" t="n">
+      <c r="H10" s="8" t="n">
         <v>46277.95163776228</v>
       </c>
-      <c r="I10" s="6" t="inlineStr">
+      <c r="I10" s="5" t="inlineStr">
         <is>
           <t>60fb3f4b52219514d8f0dc8d20c962ad2fd902dee0cf2407da91f2a93d215a37</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>G&amp;A</t>
         </is>
       </c>
-      <c r="B11" s="7" t="n">
+      <c r="B11" s="6" t="n">
         <v>585875.91</v>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>MTDC</t>
         </is>
       </c>
-      <c r="D11" s="7" t="n">
+      <c r="D11" s="6" t="n">
         <v>4736602.11</v>
       </c>
-      <c r="E11" s="8" t="n">
+      <c r="E11" s="7" t="n">
         <v>0.1237</v>
       </c>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>Tom Metzinger</t>
         </is>
       </c>
-      <c r="H11" s="9" t="n">
+      <c r="H11" s="8" t="n">
         <v>46277.95163776228</v>
       </c>
-      <c r="I11" s="6" t="inlineStr">
+      <c r="I11" s="5" t="inlineStr">
         <is>
           <t>60fb3f4b52219514d8f0dc8d20c962ad2fd902dee0cf2407da91f2a93d215a37</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>INDIRECT_COMBINED</t>
         </is>
       </c>
-      <c r="B12" s="7" t="n">
+      <c r="B12" s="6" t="n">
         <v>1170650.43</v>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>MTDC</t>
         </is>
       </c>
-      <c r="D12" s="7" t="n">
+      <c r="D12" s="6" t="n">
         <v>4736602.11</v>
       </c>
-      <c r="E12" s="8" t="n">
+      <c r="E12" s="7" t="n">
         <v>0.2471</v>
       </c>
-      <c r="F12" s="6" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
         <is>
           <t>PROPOSED</t>
         </is>
       </c>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>Tom Metzinger</t>
         </is>
       </c>
-      <c r="H12" s="9" t="n">
+      <c r="H12" s="8" t="n">
         <v>46277.95163776228</v>
       </c>
-      <c r="I12" s="6" t="inlineStr">
+      <c r="I12" s="5" t="inlineStr">
         <is>
           <t>60fb3f4b52219514d8f0dc8d20c962ad2fd902dee0cf2407da91f2a93d215a37</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="10" t="inlineStr">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>Carve-outs</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>What was removed from a pool before the rate was struck. Each one names the authority it was removed under and the driver that sized it — a reduction without both is an adjustment, not a carve-out.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>Pool</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>What</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>Authority</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>Driver</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="F17" s="4" t="inlineStr">
         <is>
           <t>Grade</t>
         </is>
       </c>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="G17" s="4" t="inlineStr">
         <is>
           <t>Recorded by</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>OVERHEAD</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>Depreciation on federally funded assets</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>2 CFR 200.436(b)</t>
         </is>
       </c>
-      <c r="D18" s="7" t="n">
+      <c r="D18" s="6" t="n">
         <v>156235.27</v>
       </c>
-      <c r="E18" s="6" t="inlineStr">
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>20 asset(s) on the fixed-asset register carry a federal funding source; the depreciation on the federally funded share of them is 156,235.27, against 850,382.89 of depreciation classified to this pool</t>
         </is>
       </c>
-      <c r="F18" s="6" t="inlineStr">
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>CORROBORATED</t>
         </is>
       </c>
-      <c r="G18" s="6" t="inlineStr">
+      <c r="G18" s="5" t="inlineStr">
         <is>
           <t>Tom Metzinger</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="6" t="inlineStr">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>OVERHEAD</t>
         </is>
       </c>
-      <c r="B19" s="6" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>Rental and vacant space — America Makes Building</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>2 CFR 200.465</t>
         </is>
       </c>
-      <c r="D19" s="7" t="n">
+      <c r="D19" s="6" t="n">
         <v>128010.25</v>
       </c>
-      <c r="E19" s="6" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>99.9% of this building is let, committed or vacant (15,429 sq ft); the building is 15,448 of the estate's 180,538</t>
         </is>
       </c>
-      <c r="F19" s="6" t="inlineStr">
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>MANAGEMENT_RECONSTRUCTION</t>
         </is>
       </c>
-      <c r="G19" s="6" t="inlineStr">
+      <c r="G19" s="5" t="inlineStr">
         <is>
           <t>Tom Metzinger</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="6" t="inlineStr">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>OVERHEAD</t>
         </is>
       </c>
-      <c r="B20" s="6" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>Rental and vacant space — Semple Building</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>2 CFR 200.465</t>
         </is>
       </c>
-      <c r="D20" s="7" t="n">
+      <c r="D20" s="6" t="n">
         <v>130300.5</v>
       </c>
-      <c r="E20" s="6" t="inlineStr">
+      <c r="E20" s="5" t="inlineStr">
         <is>
           <t>55.9% of this building is let, committed or vacant (15,705 sq ft); the building is 28,112 of the estate's 180,538</t>
         </is>
       </c>
-      <c r="F20" s="6" t="inlineStr">
+      <c r="F20" s="5" t="inlineStr">
         <is>
           <t>MANAGEMENT_RECONSTRUCTION</t>
         </is>
       </c>
-      <c r="G20" s="6" t="inlineStr">
+      <c r="G20" s="5" t="inlineStr">
         <is>
           <t>Tom Metzinger</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="6" t="inlineStr">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>OVERHEAD</t>
         </is>
       </c>
-      <c r="B21" s="6" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>Rental and vacant space — Taft Technology Center</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>2 CFR 200.465</t>
         </is>
       </c>
-      <c r="D21" s="7" t="n">
+      <c r="D21" s="6" t="n">
         <v>281002.12</v>
       </c>
-      <c r="E21" s="6" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>99.1% of this building is let, committed or vacant (33,869 sq ft); the building is 34,181 of the estate's 180,538</t>
         </is>
       </c>
-      <c r="F21" s="6" t="inlineStr">
+      <c r="F21" s="5" t="inlineStr">
         <is>
           <t>MANAGEMENT_RECONSTRUCTION</t>
         </is>
       </c>
-      <c r="G21" s="6" t="inlineStr">
+      <c r="G21" s="5" t="inlineStr">
         <is>
           <t>Tom Metzinger</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="6" t="inlineStr">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>OVERHEAD</t>
         </is>
       </c>
-      <c r="B22" s="6" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>Rental and vacant space — Tech Block Building 5</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>2 CFR 200.465</t>
         </is>
       </c>
-      <c r="D22" s="7" t="n">
+      <c r="D22" s="6" t="n">
         <v>149498.82</v>
       </c>
-      <c r="E22" s="6" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>33.2% of this building is let, committed or vacant (18,019 sq ft); the building is 54,308 of the estate's 180,538</t>
         </is>
       </c>
-      <c r="F22" s="6" t="inlineStr">
+      <c r="F22" s="5" t="inlineStr">
         <is>
           <t>MANAGEMENT_RECONSTRUCTION</t>
         </is>
       </c>
-      <c r="G22" s="6" t="inlineStr">
+      <c r="G22" s="5" t="inlineStr">
         <is>
           <t>Tom Metzinger</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="6" t="inlineStr">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>OVERHEAD</t>
         </is>
       </c>
-      <c r="B23" s="6" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>Rental and vacant space — YBI Main (Vindicator Building)</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>2 CFR 200.465</t>
         </is>
       </c>
-      <c r="D23" s="7" t="n">
+      <c r="D23" s="6" t="n">
         <v>68057.64</v>
       </c>
-      <c r="E23" s="6" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>16.9% of this building is let, committed or vacant (8,203 sq ft); the building is 48,489 of the estate's 180,538</t>
         </is>
       </c>
-      <c r="F23" s="6" t="inlineStr">
+      <c r="F23" s="5" t="inlineStr">
         <is>
           <t>MANAGEMENT_RECONSTRUCTION</t>
         </is>
       </c>
-      <c r="G23" s="6" t="inlineStr">
+      <c r="G23" s="5" t="inlineStr">
         <is>
           <t>Tom Metzinger</t>
         </is>
